--- a/énoncé/Fiche autoévaluation comparative.xlsx
+++ b/énoncé/Fiche autoévaluation comparative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Professionnel\CVM\Enseignement\2021_1_Hiver\C52\Projets\p1\_pour_etudiants\énoncé\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\KNN_project\énoncé\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505FF71F-E8A2-4DAA-A268-0CD180800A83}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD87F2A6-A506-4A56-9C32-5A92E3DA194F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3394" yWindow="3394" windowWidth="24686" windowHeight="13149" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="270" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Évaluation" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
   <si>
     <t>Étudiant 1</t>
   </si>
@@ -324,6 +324,21 @@
   </si>
   <si>
     <t>débrouillardise, initiative, amène des solutions pertinentes et de haut niveau, motivation d'équipe …</t>
+  </si>
+  <si>
+    <t>Dextraze Antoine</t>
+  </si>
+  <si>
+    <t>Chartrand Alexiane</t>
+  </si>
+  <si>
+    <t>Dilion Laurentiu</t>
+  </si>
+  <si>
+    <t>Nayaradou Irvan</t>
+  </si>
+  <si>
+    <t>Rajotte François</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1099,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
@@ -1132,7 +1147,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
@@ -1215,15 +1230,11 @@
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1274,31 +1285,31 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1337,13 +1348,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
@@ -1412,6 +1416,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection hidden="1"/>
@@ -1515,14 +1527,6 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1542,23 +1546,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0" hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF800000"/>
@@ -1567,15 +1564,6 @@
         <bottom style="thin">
           <color rgb="FF800000"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF800000"/>
-      </font>
-      <border>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1597,6 +1585,25 @@
           <color rgb="FF800000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF800000"/>
+      </font>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1623,9 +1630,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1663,7 +1670,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1769,7 +1776,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1911,7 +1918,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1920,169 +1927,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:AA80"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="49" customWidth="1"/>
-    <col min="2" max="2" width="7" style="49" customWidth="1"/>
-    <col min="3" max="3" width="3" style="49" customWidth="1"/>
-    <col min="4" max="4" width="12" style="49" customWidth="1"/>
-    <col min="5" max="5" width="18.84375" style="49" customWidth="1"/>
-    <col min="6" max="6" width="34.4609375" style="49" customWidth="1"/>
-    <col min="7" max="9" width="13.69140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.69140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.69140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.23046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.3828125" style="3" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="11.23046875" style="2" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="3" style="48" customWidth="1"/>
+    <col min="2" max="2" width="7" style="48" customWidth="1"/>
+    <col min="3" max="3" width="3" style="48" customWidth="1"/>
+    <col min="4" max="4" width="12" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="48" customWidth="1"/>
+    <col min="6" max="6" width="34.42578125" style="48" customWidth="1"/>
+    <col min="7" max="9" width="13.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="22" width="9" style="2" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="10" style="2" hidden="1" customWidth="1"/>
-    <col min="24" max="25" width="9" style="49" hidden="1" customWidth="1"/>
+    <col min="24" max="25" width="9" style="48" hidden="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="2" hidden="1" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="49"/>
+    <col min="28" max="16384" width="9" style="48"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="87" t="s">
+    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="86" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="87"/>
-      <c r="D3" s="107" t="s">
+    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="86"/>
+      <c r="D3" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109">
-        <v>3</v>
-      </c>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="110"/>
-    </row>
-    <row r="4" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="87"/>
-    </row>
-    <row r="5" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="87"/>
-      <c r="D5" s="107" t="s">
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="108">
+        <v>5</v>
+      </c>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="109"/>
+    </row>
+    <row r="4" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="86"/>
+    </row>
+    <row r="5" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="86"/>
+      <c r="D5" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="91">
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="90">
         <v>0.85</v>
       </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="92"/>
-    </row>
-    <row r="6" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="87"/>
-      <c r="G6" s="93" t="s">
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="91"/>
+    </row>
+    <row r="6" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="86"/>
+      <c r="G6" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B7" s="87"/>
-      <c r="D7" s="105" t="s">
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="86"/>
+      <c r="D7" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="94">
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="93">
         <v>0.5</v>
       </c>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="95"/>
-    </row>
-    <row r="8" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="87"/>
-      <c r="D8" s="103" t="s">
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="94"/>
+    </row>
+    <row r="8" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="86"/>
+      <c r="D8" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="96">
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="95">
         <f>1-G7</f>
         <v>0.5</v>
       </c>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="97"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="96"/>
       <c r="V8" s="4"/>
     </row>
-    <row r="9" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="87"/>
+    <row r="9" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="86"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B10" s="87"/>
-      <c r="D10" s="101" t="s">
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="97"/>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="86"/>
+      <c r="D10" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="89">
-        <v>0</v>
-      </c>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
-      <c r="K10" s="90"/>
-    </row>
-    <row r="11" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="87"/>
-      <c r="D11" s="99" t="s">
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="88">
+        <v>0</v>
+      </c>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="89"/>
+    </row>
+    <row r="11" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="86"/>
+      <c r="D11" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="113">
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="84">
         <f ca="1">V44</f>
         <v>0</v>
       </c>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="114"/>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B12" s="87"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="85"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" s="86"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="K12" s="79" t="s">
+      <c r="K12" s="76" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="88" t="s">
+    <row r="14" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="87" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="88"/>
+    <row r="15" spans="2:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="87"/>
       <c r="D15" s="21"/>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
@@ -2095,35 +2102,35 @@
       <c r="I15" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="111" t="s">
+      <c r="J15" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="K15" s="112"/>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.4">
-      <c r="B16" s="88"/>
+      <c r="K15" s="111"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" s="87"/>
       <c r="D16" s="12"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="80">
+      <c r="G16" s="77">
         <v>0.4</v>
       </c>
-      <c r="H16" s="81">
+      <c r="H16" s="78">
         <v>0.4</v>
       </c>
-      <c r="I16" s="82">
+      <c r="I16" s="79">
         <v>0.2</v>
       </c>
-      <c r="J16" s="62"/>
+      <c r="J16" s="61"/>
       <c r="K16" s="14"/>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B17" s="88"/>
+    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B17" s="87"/>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="50" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="26">
@@ -2138,13 +2145,13 @@
       <c r="J17" s="9"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="88"/>
+    <row r="18" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="87"/>
       <c r="D18" s="12"/>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="52" t="s">
+      <c r="F18" s="51" t="s">
         <v>50</v>
       </c>
       <c r="G18" s="26"/>
@@ -2153,49 +2160,53 @@
       <c r="J18" s="9"/>
       <c r="K18" s="14"/>
     </row>
-    <row r="19" spans="2:27" ht="15" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="88"/>
-      <c r="C19" s="58">
+    <row r="19" spans="2:27" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="87"/>
+      <c r="C19" s="57">
         <v>1</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="E19" s="63"/>
-      <c r="F19" s="64"/>
+      <c r="E19" s="62">
+        <v>1765983</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>96</v>
+      </c>
       <c r="G19" s="28">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="7">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I19" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="J19" s="60" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="J19" s="59" t="str">
         <f ca="1">IF(V19&gt;0,"- "&amp;TEXT(V19*100,"0.0")&amp;"%",IF(Z19&gt;0,"+ "&amp;TEXT(Z19*100,"0.0")&amp;"%",""))</f>
         <v/>
       </c>
       <c r="K19" s="16">
         <f ca="1">AA19</f>
-        <v>0.76924999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="L19" s="34"/>
-      <c r="M19" s="46">
+      <c r="M19" s="45">
         <f t="shared" ref="M19:M43" si="0">E19</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="50">
+        <v>1765983</v>
+      </c>
+      <c r="N19" s="49">
         <f t="array" ref="N19">SUM(G19:I19/$G$17:$I$17*$G$16:$I$16)</f>
-        <v>0.27</v>
-      </c>
-      <c r="O19" s="50">
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="O19" s="49">
         <f>1/$M$49</f>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P19" s="4">
         <f>N19/O19</f>
-        <v>0.81</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Q19" s="4">
         <f>$G$5</f>
@@ -2207,15 +2218,15 @@
       </c>
       <c r="S19" s="4">
         <f>P19*Q19*$G$8</f>
-        <v>0.34425</v>
+        <v>0.4250000000000001</v>
       </c>
       <c r="T19" s="4">
         <f>SUM(R19:S19)</f>
-        <v>0.76924999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="U19" s="4">
         <f>MIN(1,T19)</f>
-        <v>0.76924999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="V19" s="4">
         <f>T19-U19</f>
@@ -2223,11 +2234,11 @@
       </c>
       <c r="W19" s="4">
         <f>1-U19</f>
-        <v>0.23075000000000001</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="X19" s="4">
         <f ca="1">W19/$W$44</f>
-        <v>0.51277777777777789</v>
+        <v>0.2</v>
       </c>
       <c r="Y19" s="4">
         <f ca="1">X19*$V$44</f>
@@ -2239,52 +2250,56 @@
       </c>
       <c r="AA19" s="4">
         <f ca="1">U19+Z19</f>
-        <v>0.76924999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B20" s="88"/>
-      <c r="C20" s="58">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B20" s="87"/>
+      <c r="C20" s="57">
         <v>2</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
+      <c r="E20" s="64">
+        <v>1759119</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>97</v>
+      </c>
       <c r="G20" s="30">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="H20" s="8">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I20" s="31">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J20" s="61" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="J20" s="60" t="str">
         <f t="shared" ref="J20:J43" ca="1" si="1">IF(V20&gt;0,"- "&amp;TEXT(V20*100,"0.0")&amp;"%",IF(Z20&gt;0,"+ "&amp;TEXT(Z20*100,"0.0")&amp;"%",""))</f>
         <v/>
       </c>
       <c r="K20" s="18">
         <f t="shared" ref="K20:K43" ca="1" si="2">AA20</f>
-        <v>0.99875000000000003</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="L20" s="34"/>
-      <c r="M20" s="46">
+      <c r="M20" s="45">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="50">
+        <v>1759119</v>
+      </c>
+      <c r="N20" s="49">
         <f t="array" ref="N20">SUM(G20:I20/$G$17:$I$17*$G$16:$I$16)</f>
-        <v>0.45000000000000007</v>
-      </c>
-      <c r="O20" s="50">
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="O20" s="49">
         <f>1/$M$49</f>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P20" s="4">
         <f>N20/O20</f>
-        <v>1.3500000000000003</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Q20" s="4">
         <f>$G$5</f>
@@ -2296,15 +2311,15 @@
       </c>
       <c r="S20" s="4">
         <f>P20*Q20*$G$8</f>
-        <v>0.57375000000000009</v>
+        <v>0.4250000000000001</v>
       </c>
       <c r="T20" s="4">
         <f t="shared" ref="T20:T22" si="3">SUM(R20:S20)</f>
-        <v>0.99875000000000003</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="U20" s="4">
         <f>MIN(1,T20)</f>
-        <v>0.99875000000000003</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" ref="V20:V22" si="4">T20-U20</f>
@@ -2312,11 +2327,11 @@
       </c>
       <c r="W20" s="4">
         <f>1-U20</f>
-        <v>1.2499999999999734E-3</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="X20" s="4">
         <f ca="1">W20/$W$44</f>
-        <v>2.7777777777777189E-3</v>
+        <v>0.2</v>
       </c>
       <c r="Y20" s="4">
         <f ca="1">X20*$V$44</f>
@@ -2328,52 +2343,56 @@
       </c>
       <c r="AA20" s="4">
         <f ca="1">U20+Z20</f>
-        <v>0.99875000000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B21" s="88"/>
-      <c r="C21" s="58">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B21" s="87"/>
+      <c r="C21" s="57">
         <v>3</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="65"/>
-      <c r="F21" s="66"/>
+      <c r="E21" s="64">
+        <v>2239131</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>98</v>
+      </c>
       <c r="G21" s="30">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H21" s="8">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I21" s="31">
         <v>0.2</v>
       </c>
-      <c r="J21" s="61" t="str">
+      <c r="J21" s="60" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="K21" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78200000000000003</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="L21" s="34"/>
-      <c r="M21" s="46">
+      <c r="M21" s="45">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="50">
+        <v>2239131</v>
+      </c>
+      <c r="N21" s="49">
         <f t="array" ref="N21">SUM(G21:I21/$G$17:$I$17*$G$16:$I$16)</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="O21" s="50">
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="O21" s="49">
         <f>1/$M$49</f>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P21" s="4">
         <f>N21/O21</f>
-        <v>0.84000000000000008</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Q21" s="4">
         <f>$G$5</f>
@@ -2385,15 +2404,15 @@
       </c>
       <c r="S21" s="4">
         <f>P21*Q21*$G$8</f>
-        <v>0.35700000000000004</v>
+        <v>0.4250000000000001</v>
       </c>
       <c r="T21" s="4">
         <f t="shared" si="3"/>
-        <v>0.78200000000000003</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="U21" s="4">
         <f>MIN(1,T21)</f>
-        <v>0.78200000000000003</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="4"/>
@@ -2401,11 +2420,11 @@
       </c>
       <c r="W21" s="4">
         <f>1-U21</f>
-        <v>0.21799999999999997</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="X21" s="4">
         <f ca="1">W21/$W$44</f>
-        <v>0.48444444444444446</v>
+        <v>0.2</v>
       </c>
       <c r="Y21" s="4">
         <f ca="1">X21*$V$44</f>
@@ -2417,46 +2436,54 @@
       </c>
       <c r="AA21" s="4">
         <f ca="1">U21+Z21</f>
-        <v>0.78200000000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B22" s="88"/>
-      <c r="C22" s="58">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B22" s="87"/>
+      <c r="C22" s="57">
         <v>4</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="65"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="61" t="str">
+      <c r="F22" s="117" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="30">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="I22" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="J22" s="60" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
       <c r="K22" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>0.42499999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="L22" s="34"/>
-      <c r="M22" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="50">
+      <c r="M22" s="45" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N22" s="49">
         <f t="array" ref="N22">SUM(G22:I22/$G$17:$I$17*$G$16:$I$16)</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="50">
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="O22" s="49">
         <f>1/$M$49</f>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P22" s="4">
         <f>N22/O22</f>
-        <v>0</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Q22" s="4">
         <f>$G$5</f>
@@ -2468,15 +2495,15 @@
       </c>
       <c r="S22" s="4">
         <f>P22*Q22*$G$8</f>
-        <v>0</v>
+        <v>0.4250000000000001</v>
       </c>
       <c r="T22" s="4">
         <f t="shared" si="3"/>
-        <v>0.42499999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="U22" s="4">
         <f>MIN(1,T22)</f>
-        <v>0.42499999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="4"/>
@@ -2484,11 +2511,11 @@
       </c>
       <c r="W22" s="4">
         <f>1-U22</f>
-        <v>0.57499999999999996</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="X22" s="4">
         <f ca="1">W22/$W$44</f>
-        <v>1.2777777777777779</v>
+        <v>0.2</v>
       </c>
       <c r="Y22" s="4">
         <f ca="1">X22*$V$44</f>
@@ -2500,46 +2527,56 @@
       </c>
       <c r="AA22" s="4">
         <f ca="1">U22+Z22</f>
-        <v>0.42499999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="88"/>
-      <c r="C23" s="58">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B23" s="87"/>
+      <c r="C23" s="57">
         <v>5</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="65"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="77" t="str">
+      <c r="E23" s="64">
+        <v>6242723</v>
+      </c>
+      <c r="F23" s="65" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="30">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="I23" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="J23" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="78">
+      <c r="K23" s="75">
         <f t="shared" ca="1" si="2"/>
-        <v>0.42499999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="L23" s="34"/>
-      <c r="M23" s="46">
+      <c r="M23" s="45">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="68">
+        <v>6242723</v>
+      </c>
+      <c r="N23" s="49">
         <f t="array" ref="N23">SUM(G23:I23/$G$17:$I$17*$G$16:$I$16)</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="68">
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="O23" s="49">
         <f t="shared" ref="O23:O43" si="6">1/$M$49</f>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" ref="P23:P43" si="7">N23/O23</f>
-        <v>0</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" ref="Q23:Q43" si="8">$G$5</f>
@@ -2551,15 +2588,15 @@
       </c>
       <c r="S23" s="4">
         <f t="shared" ref="S23:S43" si="10">P23*Q23*$G$8</f>
-        <v>0</v>
+        <v>0.4250000000000001</v>
       </c>
       <c r="T23" s="4">
         <f t="shared" ref="T23:T43" si="11">SUM(R23:S23)</f>
-        <v>0.42499999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="U23" s="4">
         <f t="shared" ref="U23:U43" si="12">MIN(1,T23)</f>
-        <v>0.42499999999999999</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" ref="V23:V43" si="13">T23-U23</f>
@@ -2567,11 +2604,11 @@
       </c>
       <c r="W23" s="4">
         <f t="shared" ref="W23:W43" si="14">1-U23</f>
-        <v>0.57499999999999996</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="X23" s="4">
         <f t="shared" ref="X23:X43" ca="1" si="15">W23/$W$44</f>
-        <v>1.2777777777777779</v>
+        <v>0.2</v>
       </c>
       <c r="Y23" s="4">
         <f t="shared" ref="Y23:Y43" ca="1" si="16">X23*$V$44</f>
@@ -2583,42 +2620,42 @@
       </c>
       <c r="AA23" s="4">
         <f t="shared" ref="AA23:AA43" ca="1" si="18">U23+Z23</f>
-        <v>0.42499999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="88"/>
-      <c r="C24" s="58">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B24" s="87"/>
+      <c r="C24" s="57">
         <v>6</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="65"/>
-      <c r="F24" s="66"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="65"/>
       <c r="G24" s="30"/>
       <c r="H24" s="8"/>
       <c r="I24" s="31"/>
-      <c r="J24" s="77" t="str">
+      <c r="J24" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="78">
+      <c r="K24" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L24" s="34"/>
-      <c r="M24" s="46">
+      <c r="M24" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N24" s="68">
+      <c r="N24" s="49">
         <f t="array" ref="N24">SUM(G24:I24/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="68">
+      <c r="O24" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="7"/>
@@ -2654,7 +2691,7 @@
       </c>
       <c r="X24" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y24" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2669,39 +2706,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="25" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="88"/>
-      <c r="C25" s="58">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B25" s="87"/>
+      <c r="C25" s="57">
         <v>7</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="65"/>
       <c r="G25" s="30"/>
       <c r="H25" s="8"/>
       <c r="I25" s="31"/>
-      <c r="J25" s="77" t="str">
+      <c r="J25" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="78">
+      <c r="K25" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L25" s="34"/>
-      <c r="M25" s="46">
+      <c r="M25" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N25" s="68">
+      <c r="N25" s="49">
         <f t="array" ref="N25">SUM(G25:I25/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="68">
+      <c r="O25" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P25" s="4">
         <f t="shared" si="7"/>
@@ -2737,7 +2774,7 @@
       </c>
       <c r="X25" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y25" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2752,39 +2789,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="26" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="88"/>
-      <c r="C26" s="58">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B26" s="87"/>
+      <c r="C26" s="57">
         <v>8</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="65"/>
-      <c r="F26" s="66"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="65"/>
       <c r="G26" s="30"/>
       <c r="H26" s="8"/>
       <c r="I26" s="31"/>
-      <c r="J26" s="77" t="str">
+      <c r="J26" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="78">
+      <c r="K26" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L26" s="34"/>
-      <c r="M26" s="46">
+      <c r="M26" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N26" s="68">
+      <c r="N26" s="49">
         <f t="array" ref="N26">SUM(G26:I26/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="68">
+      <c r="O26" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P26" s="4">
         <f t="shared" si="7"/>
@@ -2820,7 +2857,7 @@
       </c>
       <c r="X26" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y26" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2835,39 +2872,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="27" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="88"/>
-      <c r="C27" s="58">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B27" s="87"/>
+      <c r="C27" s="57">
         <v>9</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="65"/>
       <c r="G27" s="30"/>
       <c r="H27" s="8"/>
       <c r="I27" s="31"/>
-      <c r="J27" s="77" t="str">
+      <c r="J27" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="78">
+      <c r="K27" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L27" s="34"/>
-      <c r="M27" s="46">
+      <c r="M27" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="68">
+      <c r="N27" s="49">
         <f t="array" ref="N27">SUM(G27:I27/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O27" s="68">
+      <c r="O27" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P27" s="4">
         <f t="shared" si="7"/>
@@ -2903,7 +2940,7 @@
       </c>
       <c r="X27" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y27" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -2918,39 +2955,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="28" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="88"/>
-      <c r="C28" s="58">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B28" s="87"/>
+      <c r="C28" s="57">
         <v>10</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="65"/>
-      <c r="F28" s="66"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="65"/>
       <c r="G28" s="30"/>
       <c r="H28" s="8"/>
       <c r="I28" s="31"/>
-      <c r="J28" s="77" t="str">
+      <c r="J28" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="78">
+      <c r="K28" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L28" s="34"/>
-      <c r="M28" s="46">
+      <c r="M28" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N28" s="68">
+      <c r="N28" s="49">
         <f t="array" ref="N28">SUM(G28:I28/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O28" s="68">
+      <c r="O28" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P28" s="4">
         <f t="shared" si="7"/>
@@ -2986,7 +3023,7 @@
       </c>
       <c r="X28" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y28" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3001,39 +3038,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="29" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="88"/>
-      <c r="C29" s="58">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B29" s="87"/>
+      <c r="C29" s="57">
         <v>11</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="66"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="65"/>
       <c r="G29" s="30"/>
       <c r="H29" s="8"/>
       <c r="I29" s="31"/>
-      <c r="J29" s="77" t="str">
+      <c r="J29" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="78">
+      <c r="K29" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L29" s="34"/>
-      <c r="M29" s="46">
+      <c r="M29" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N29" s="68">
+      <c r="N29" s="49">
         <f t="array" ref="N29">SUM(G29:I29/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O29" s="68">
+      <c r="O29" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P29" s="4">
         <f t="shared" si="7"/>
@@ -3069,7 +3106,7 @@
       </c>
       <c r="X29" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y29" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3084,39 +3121,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="88"/>
-      <c r="C30" s="58">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B30" s="87"/>
+      <c r="C30" s="57">
         <v>12</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="65"/>
-      <c r="F30" s="66"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="65"/>
       <c r="G30" s="30"/>
       <c r="H30" s="8"/>
       <c r="I30" s="31"/>
-      <c r="J30" s="77" t="str">
+      <c r="J30" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="78">
+      <c r="K30" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L30" s="34"/>
-      <c r="M30" s="46">
+      <c r="M30" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N30" s="68">
+      <c r="N30" s="49">
         <f t="array" ref="N30">SUM(G30:I30/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O30" s="68">
+      <c r="O30" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P30" s="4">
         <f t="shared" si="7"/>
@@ -3152,7 +3189,7 @@
       </c>
       <c r="X30" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y30" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3167,39 +3204,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="31" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="88"/>
-      <c r="C31" s="58">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B31" s="87"/>
+      <c r="C31" s="57">
         <v>13</v>
       </c>
       <c r="D31" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="65"/>
-      <c r="F31" s="66"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="65"/>
       <c r="G31" s="30"/>
       <c r="H31" s="8"/>
       <c r="I31" s="31"/>
-      <c r="J31" s="77" t="str">
+      <c r="J31" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="78">
+      <c r="K31" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L31" s="34"/>
-      <c r="M31" s="46">
+      <c r="M31" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N31" s="68">
+      <c r="N31" s="49">
         <f t="array" ref="N31">SUM(G31:I31/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O31" s="68">
+      <c r="O31" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P31" s="4">
         <f t="shared" si="7"/>
@@ -3235,7 +3272,7 @@
       </c>
       <c r="X31" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3250,39 +3287,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="32" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="88"/>
-      <c r="C32" s="58">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B32" s="87"/>
+      <c r="C32" s="57">
         <v>14</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E32" s="65"/>
-      <c r="F32" s="66"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="65"/>
       <c r="G32" s="30"/>
       <c r="H32" s="8"/>
       <c r="I32" s="31"/>
-      <c r="J32" s="77" t="str">
+      <c r="J32" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="78">
+      <c r="K32" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L32" s="34"/>
-      <c r="M32" s="46">
+      <c r="M32" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N32" s="68">
+      <c r="N32" s="49">
         <f t="array" ref="N32">SUM(G32:I32/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O32" s="68">
+      <c r="O32" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P32" s="4">
         <f t="shared" si="7"/>
@@ -3318,7 +3355,7 @@
       </c>
       <c r="X32" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y32" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3333,39 +3370,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="33" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="88"/>
-      <c r="C33" s="58">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B33" s="87"/>
+      <c r="C33" s="57">
         <v>15</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="65"/>
-      <c r="F33" s="66"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="65"/>
       <c r="G33" s="30"/>
       <c r="H33" s="8"/>
       <c r="I33" s="31"/>
-      <c r="J33" s="77" t="str">
+      <c r="J33" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="78">
+      <c r="K33" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L33" s="34"/>
-      <c r="M33" s="46">
+      <c r="M33" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N33" s="68">
+      <c r="N33" s="49">
         <f t="array" ref="N33">SUM(G33:I33/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O33" s="68">
+      <c r="O33" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P33" s="4">
         <f t="shared" si="7"/>
@@ -3401,7 +3438,7 @@
       </c>
       <c r="X33" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y33" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3416,39 +3453,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="88"/>
-      <c r="C34" s="58">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B34" s="87"/>
+      <c r="C34" s="57">
         <v>16</v>
       </c>
       <c r="D34" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E34" s="65"/>
-      <c r="F34" s="66"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="65"/>
       <c r="G34" s="30"/>
       <c r="H34" s="8"/>
       <c r="I34" s="31"/>
-      <c r="J34" s="77" t="str">
+      <c r="J34" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="78">
+      <c r="K34" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L34" s="34"/>
-      <c r="M34" s="46">
+      <c r="M34" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N34" s="68">
+      <c r="N34" s="49">
         <f t="array" ref="N34">SUM(G34:I34/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O34" s="68">
+      <c r="O34" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P34" s="4">
         <f t="shared" si="7"/>
@@ -3484,7 +3521,7 @@
       </c>
       <c r="X34" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y34" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3499,39 +3536,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="35" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="88"/>
-      <c r="C35" s="58">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B35" s="87"/>
+      <c r="C35" s="57">
         <v>17</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="66"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="65"/>
       <c r="G35" s="30"/>
       <c r="H35" s="8"/>
       <c r="I35" s="31"/>
-      <c r="J35" s="77" t="str">
+      <c r="J35" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="78">
+      <c r="K35" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L35" s="34"/>
-      <c r="M35" s="46">
+      <c r="M35" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N35" s="68">
+      <c r="N35" s="49">
         <f t="array" ref="N35">SUM(G35:I35/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O35" s="68">
+      <c r="O35" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P35" s="4">
         <f t="shared" si="7"/>
@@ -3567,7 +3604,7 @@
       </c>
       <c r="X35" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y35" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3582,39 +3619,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="36" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="88"/>
-      <c r="C36" s="58">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B36" s="87"/>
+      <c r="C36" s="57">
         <v>18</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="65"/>
-      <c r="F36" s="66"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65"/>
       <c r="G36" s="30"/>
       <c r="H36" s="8"/>
       <c r="I36" s="31"/>
-      <c r="J36" s="77" t="str">
+      <c r="J36" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="78">
+      <c r="K36" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L36" s="34"/>
-      <c r="M36" s="46">
+      <c r="M36" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N36" s="68">
+      <c r="N36" s="49">
         <f t="array" ref="N36">SUM(G36:I36/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O36" s="68">
+      <c r="O36" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P36" s="4">
         <f t="shared" si="7"/>
@@ -3650,7 +3687,7 @@
       </c>
       <c r="X36" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y36" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3665,39 +3702,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="37" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="88"/>
-      <c r="C37" s="58">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B37" s="87"/>
+      <c r="C37" s="57">
         <v>19</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="65"/>
-      <c r="F37" s="66"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="65"/>
       <c r="G37" s="30"/>
       <c r="H37" s="8"/>
       <c r="I37" s="31"/>
-      <c r="J37" s="77" t="str">
+      <c r="J37" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="78">
+      <c r="K37" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L37" s="34"/>
-      <c r="M37" s="46">
+      <c r="M37" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N37" s="68">
+      <c r="N37" s="49">
         <f t="array" ref="N37">SUM(G37:I37/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O37" s="68">
+      <c r="O37" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P37" s="4">
         <f t="shared" si="7"/>
@@ -3733,7 +3770,7 @@
       </c>
       <c r="X37" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y37" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3748,39 +3785,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="38" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="88"/>
-      <c r="C38" s="58">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B38" s="87"/>
+      <c r="C38" s="57">
         <v>20</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="65"/>
-      <c r="F38" s="66"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="65"/>
       <c r="G38" s="30"/>
       <c r="H38" s="8"/>
       <c r="I38" s="31"/>
-      <c r="J38" s="77" t="str">
+      <c r="J38" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="78">
+      <c r="K38" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L38" s="34"/>
-      <c r="M38" s="46">
+      <c r="M38" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N38" s="68">
+      <c r="N38" s="49">
         <f t="array" ref="N38">SUM(G38:I38/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O38" s="68">
+      <c r="O38" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P38" s="4">
         <f t="shared" si="7"/>
@@ -3816,7 +3853,7 @@
       </c>
       <c r="X38" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y38" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3831,39 +3868,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="88"/>
-      <c r="C39" s="58">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B39" s="87"/>
+      <c r="C39" s="57">
         <v>21</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E39" s="65"/>
-      <c r="F39" s="66"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="65"/>
       <c r="G39" s="30"/>
       <c r="H39" s="8"/>
       <c r="I39" s="31"/>
-      <c r="J39" s="77" t="str">
+      <c r="J39" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="78">
+      <c r="K39" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L39" s="34"/>
-      <c r="M39" s="46">
+      <c r="M39" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N39" s="68">
+      <c r="N39" s="49">
         <f t="array" ref="N39">SUM(G39:I39/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O39" s="68">
+      <c r="O39" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P39" s="4">
         <f t="shared" si="7"/>
@@ -3899,7 +3936,7 @@
       </c>
       <c r="X39" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y39" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3914,39 +3951,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="88"/>
-      <c r="C40" s="58">
+    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B40" s="87"/>
+      <c r="C40" s="57">
         <v>22</v>
       </c>
       <c r="D40" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E40" s="65"/>
-      <c r="F40" s="66"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="65"/>
       <c r="G40" s="30"/>
       <c r="H40" s="8"/>
       <c r="I40" s="31"/>
-      <c r="J40" s="77" t="str">
+      <c r="J40" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="78">
+      <c r="K40" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L40" s="34"/>
-      <c r="M40" s="46">
+      <c r="M40" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N40" s="68">
+      <c r="N40" s="49">
         <f t="array" ref="N40">SUM(G40:I40/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O40" s="68">
+      <c r="O40" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P40" s="4">
         <f t="shared" si="7"/>
@@ -3982,7 +4019,7 @@
       </c>
       <c r="X40" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y40" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -3997,39 +4034,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="41" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="88"/>
-      <c r="C41" s="58">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B41" s="87"/>
+      <c r="C41" s="57">
         <v>23</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E41" s="65"/>
-      <c r="F41" s="66"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="65"/>
       <c r="G41" s="30"/>
       <c r="H41" s="8"/>
       <c r="I41" s="31"/>
-      <c r="J41" s="77" t="str">
+      <c r="J41" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="78">
+      <c r="K41" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L41" s="34"/>
-      <c r="M41" s="46">
+      <c r="M41" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N41" s="68">
+      <c r="N41" s="49">
         <f t="array" ref="N41">SUM(G41:I41/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O41" s="68">
+      <c r="O41" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P41" s="4">
         <f t="shared" si="7"/>
@@ -4065,7 +4102,7 @@
       </c>
       <c r="X41" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y41" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -4080,39 +4117,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="42" spans="2:27" s="67" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="88"/>
-      <c r="C42" s="58">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B42" s="87"/>
+      <c r="C42" s="57">
         <v>24</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E42" s="65"/>
-      <c r="F42" s="66"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="65"/>
       <c r="G42" s="30"/>
       <c r="H42" s="8"/>
       <c r="I42" s="31"/>
-      <c r="J42" s="77" t="str">
+      <c r="J42" s="74" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="78">
+      <c r="K42" s="75">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L42" s="34"/>
-      <c r="M42" s="46">
+      <c r="M42" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N42" s="68">
+      <c r="N42" s="49">
         <f t="array" ref="N42">SUM(G42:I42/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O42" s="68">
+      <c r="O42" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P42" s="4">
         <f t="shared" si="7"/>
@@ -4148,7 +4185,7 @@
       </c>
       <c r="X42" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y42" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -4163,39 +4200,39 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="43" spans="2:27" s="67" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="88"/>
-      <c r="C43" s="58">
+    <row r="43" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="87"/>
+      <c r="C43" s="57">
         <v>25</v>
       </c>
-      <c r="D43" s="69" t="s">
+      <c r="D43" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="E43" s="70"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="74"/>
-      <c r="J43" s="75" t="str">
+      <c r="E43" s="67"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="72" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="76">
+      <c r="K43" s="73">
         <f t="shared" ca="1" si="2"/>
         <v>0.42499999999999999</v>
       </c>
       <c r="L43" s="34"/>
-      <c r="M43" s="46">
+      <c r="M43" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N43" s="68">
+      <c r="N43" s="49">
         <f t="array" ref="N43">SUM(G43:I43/$G$17:$I$17*$G$16:$I$16)</f>
         <v>0</v>
       </c>
-      <c r="O43" s="68">
+      <c r="O43" s="49">
         <f t="shared" si="6"/>
-        <v>0.33333333333333331</v>
+        <v>0.2</v>
       </c>
       <c r="P43" s="4">
         <f t="shared" si="7"/>
@@ -4231,7 +4268,7 @@
       </c>
       <c r="X43" s="4">
         <f t="shared" ca="1" si="15"/>
-        <v>1.2777777777777779</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="Y43" s="4">
         <f t="shared" ca="1" si="16"/>
@@ -4246,8 +4283,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="44" spans="2:27" ht="15.45" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B44" s="88"/>
+    <row r="44" spans="2:27" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="87"/>
       <c r="D44" s="19"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
@@ -4274,11 +4311,11 @@
       </c>
       <c r="N44" s="4">
         <f>SUM(N19:N22)</f>
-        <v>1</v>
+        <v>0.80000000000000016</v>
       </c>
       <c r="O44" s="4">
         <f>SUM(O19:O22)</f>
-        <v>1.3333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
@@ -4292,19 +4329,18 @@
       </c>
       <c r="W44" s="4">
         <f ca="1">SUM(OFFSET(W19, 0, 0, $G$3, 1))</f>
-        <v>0.44999999999999996</v>
+        <v>0.74999999999999956</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" s="2"/>
     </row>
-    <row r="45" spans="2:27" s="6" customFormat="1" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="88"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="37"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="36"/>
+    <row r="45" spans="2:27" s="6" customFormat="1" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="87"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="L45" s="35"/>
       <c r="M45" s="5" t="s">
         <v>36</v>
       </c>
@@ -4312,7 +4348,7 @@
       <c r="O45" s="2"/>
       <c r="P45" s="4">
         <f>AVERAGE(P19:P22)</f>
-        <v>0.75</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Q45" s="4">
         <f>AVERAGE(Q19:Q22)</f>
@@ -4324,37 +4360,36 @@
       </c>
       <c r="S45" s="4">
         <f t="shared" si="20"/>
-        <v>0.31875000000000003</v>
+        <v>0.4250000000000001</v>
       </c>
       <c r="T45" s="4">
         <f>AVERAGE(T19:T22)</f>
-        <v>0.74374999999999991</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="U45" s="4">
         <f>AVERAGE(U19:U22)</f>
-        <v>0.74374999999999991</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="V45" s="4"/>
       <c r="W45" s="2"/>
       <c r="X45" s="4"/>
-      <c r="Y45" s="49"/>
+      <c r="Y45" s="48"/>
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="2:27" s="6" customFormat="1" ht="12.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="55"/>
-      <c r="G46" s="57" t="s">
+    <row r="46" spans="2:27" s="6" customFormat="1" ht="12.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="54"/>
+      <c r="G46" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="H46" s="57" t="s">
+      <c r="H46" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="57" t="s">
+      <c r="I46" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="J46" s="57"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="36"/>
+      <c r="J46" s="56"/>
+      <c r="L46" s="35"/>
       <c r="M46" s="5"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -4367,26 +4402,25 @@
       <c r="V46" s="4"/>
       <c r="W46" s="2"/>
       <c r="X46" s="4"/>
-      <c r="Y46" s="49"/>
+      <c r="Y46" s="48"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="2:27" s="6" customFormat="1" ht="31.2" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="G47" s="56" t="str">
+    <row r="47" spans="2:27" s="6" customFormat="1" ht="31.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G47" s="55" t="str">
         <f ca="1">IF(G44&lt;&gt;1,"La somme doit être égale à 100%","")</f>
         <v/>
       </c>
-      <c r="H47" s="56" t="str">
+      <c r="H47" s="55" t="str">
         <f t="shared" ref="H47:I47" ca="1" si="21">IF(H44&lt;&gt;1,"La somme doit être égale à 100%","")</f>
         <v/>
       </c>
-      <c r="I47" s="56" t="str">
+      <c r="I47" s="55" t="str">
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
-      <c r="J47" s="56"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="36"/>
+      <c r="J47" s="55"/>
+      <c r="L47" s="35"/>
       <c r="M47" s="3"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -4398,551 +4432,551 @@
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
-      <c r="X47" s="49"/>
-      <c r="Y47" s="49"/>
+      <c r="X47" s="48"/>
+      <c r="Y47" s="48"/>
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="2:27" s="6" customFormat="1" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="37"/>
-      <c r="K48" s="35"/>
-      <c r="L48" s="36"/>
-      <c r="M48" s="47" t="s">
+    <row r="48" spans="2:27" s="6" customFormat="1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="L48" s="35"/>
+      <c r="M48" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="N48" s="47" t="s">
+      <c r="N48" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="O48" s="47" t="s">
+      <c r="O48" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="P48" s="47" t="s">
+      <c r="P48" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="Q48" s="47" t="s">
+      <c r="Q48" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="R48" s="47" t="s">
+      <c r="R48" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="S48" s="47" t="s">
+      <c r="S48" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="T48" s="47" t="s">
+      <c r="T48" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="U48" s="47" t="s">
+      <c r="U48" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="V48" s="47" t="s">
+      <c r="V48" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="W48" s="47" t="s">
+      <c r="W48" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="X48" s="47" t="s">
+      <c r="X48" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="Y48" s="47" t="s">
+      <c r="Y48" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="Z48" s="47" t="s">
+      <c r="Z48" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="AA48" s="47" t="s">
+      <c r="AA48" s="46" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="38" t="s">
+    <row r="49" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L49" s="38"/>
-      <c r="M49" s="59">
+      <c r="L49" s="37"/>
+      <c r="M49" s="58">
         <f>G3</f>
-        <v>3</v>
-      </c>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="41"/>
-      <c r="X49" s="44"/>
-      <c r="Y49" s="44"/>
-      <c r="Z49" s="41"/>
-      <c r="AA49" s="41"/>
-    </row>
-    <row r="50" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E50" s="48"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="40"/>
+      <c r="O49" s="40"/>
+      <c r="P49" s="40"/>
+      <c r="Q49" s="40"/>
+      <c r="R49" s="40"/>
+      <c r="S49" s="40"/>
+      <c r="T49" s="40"/>
+      <c r="U49" s="40"/>
+      <c r="V49" s="40"/>
+      <c r="W49" s="40"/>
+      <c r="X49" s="43"/>
+      <c r="Y49" s="43"/>
+      <c r="Z49" s="40"/>
+      <c r="AA49" s="40"/>
+    </row>
+    <row r="50" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="47"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="L50" s="38"/>
-      <c r="M50" s="39"/>
-      <c r="N50" s="42"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="41"/>
-      <c r="S50" s="41"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
-      <c r="W50" s="41"/>
-      <c r="X50" s="44"/>
-      <c r="Y50" s="44"/>
-      <c r="Z50" s="41"/>
-      <c r="AA50" s="41"/>
-    </row>
-    <row r="51" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E51" s="48"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="38" t="s">
+      <c r="L50" s="37"/>
+      <c r="M50" s="38"/>
+      <c r="N50" s="41"/>
+      <c r="O50" s="40"/>
+      <c r="P50" s="40"/>
+      <c r="Q50" s="40"/>
+      <c r="R50" s="40"/>
+      <c r="S50" s="40"/>
+      <c r="T50" s="40"/>
+      <c r="U50" s="40"/>
+      <c r="V50" s="40"/>
+      <c r="W50" s="40"/>
+      <c r="X50" s="43"/>
+      <c r="Y50" s="43"/>
+      <c r="Z50" s="40"/>
+      <c r="AA50" s="40"/>
+    </row>
+    <row r="51" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="47"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="39"/>
+      <c r="K51" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="L51" s="38"/>
-      <c r="M51" s="39"/>
-      <c r="N51" s="40"/>
-      <c r="O51" s="42"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="41"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="41"/>
-      <c r="W51" s="41"/>
-      <c r="X51" s="44"/>
-      <c r="Y51" s="44"/>
-      <c r="Z51" s="41"/>
-      <c r="AA51" s="41"/>
-    </row>
-    <row r="52" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E52" s="48"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="38" t="s">
+      <c r="L51" s="37"/>
+      <c r="M51" s="38"/>
+      <c r="N51" s="39"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="40"/>
+      <c r="R51" s="40"/>
+      <c r="S51" s="40"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="40"/>
+      <c r="V51" s="40"/>
+      <c r="W51" s="40"/>
+      <c r="X51" s="43"/>
+      <c r="Y51" s="43"/>
+      <c r="Z51" s="40"/>
+      <c r="AA51" s="40"/>
+    </row>
+    <row r="52" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="47"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="38"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="40"/>
-      <c r="O52" s="40"/>
-      <c r="P52" s="42"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="41"/>
-      <c r="S52" s="41"/>
-      <c r="T52" s="41"/>
-      <c r="U52" s="41"/>
-      <c r="V52" s="41"/>
-      <c r="W52" s="41"/>
-      <c r="X52" s="44"/>
-      <c r="Y52" s="44"/>
-      <c r="Z52" s="41"/>
-      <c r="AA52" s="41"/>
-    </row>
-    <row r="53" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E53" s="48"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="38" t="s">
+      <c r="L52" s="37"/>
+      <c r="M52" s="38"/>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="41"/>
+      <c r="Q52" s="40"/>
+      <c r="R52" s="40"/>
+      <c r="S52" s="40"/>
+      <c r="T52" s="40"/>
+      <c r="U52" s="40"/>
+      <c r="V52" s="40"/>
+      <c r="W52" s="40"/>
+      <c r="X52" s="43"/>
+      <c r="Y52" s="43"/>
+      <c r="Z52" s="40"/>
+      <c r="AA52" s="40"/>
+    </row>
+    <row r="53" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E53" s="47"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="39"/>
+      <c r="K53" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="L53" s="38"/>
-      <c r="M53" s="39"/>
-      <c r="N53" s="40"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="40"/>
-      <c r="Q53" s="42"/>
-      <c r="R53" s="41"/>
-      <c r="S53" s="41"/>
-      <c r="T53" s="41"/>
-      <c r="U53" s="41"/>
-      <c r="V53" s="41"/>
-      <c r="W53" s="41"/>
-      <c r="X53" s="44"/>
-      <c r="Y53" s="44"/>
-      <c r="Z53" s="41"/>
-      <c r="AA53" s="41"/>
-    </row>
-    <row r="54" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E54" s="48"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="43"/>
-      <c r="J54" s="43"/>
-      <c r="K54" s="38" t="s">
+      <c r="L53" s="37"/>
+      <c r="M53" s="38"/>
+      <c r="N53" s="39"/>
+      <c r="O53" s="39"/>
+      <c r="P53" s="39"/>
+      <c r="Q53" s="41"/>
+      <c r="R53" s="40"/>
+      <c r="S53" s="40"/>
+      <c r="T53" s="40"/>
+      <c r="U53" s="40"/>
+      <c r="V53" s="40"/>
+      <c r="W53" s="40"/>
+      <c r="X53" s="43"/>
+      <c r="Y53" s="43"/>
+      <c r="Z53" s="40"/>
+      <c r="AA53" s="40"/>
+    </row>
+    <row r="54" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E54" s="47"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="L54" s="38"/>
-      <c r="M54" s="39"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="40"/>
-      <c r="P54" s="40"/>
-      <c r="Q54" s="40"/>
-      <c r="R54" s="42"/>
-      <c r="S54" s="41"/>
-      <c r="T54" s="41"/>
-      <c r="U54" s="41"/>
-      <c r="V54" s="41"/>
-      <c r="W54" s="41"/>
-      <c r="X54" s="44"/>
-      <c r="Y54" s="44"/>
-      <c r="Z54" s="41"/>
-      <c r="AA54" s="41"/>
-    </row>
-    <row r="55" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E55" s="48"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="38" t="s">
+      <c r="L54" s="37"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="39"/>
+      <c r="O54" s="39"/>
+      <c r="P54" s="39"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="41"/>
+      <c r="S54" s="40"/>
+      <c r="T54" s="40"/>
+      <c r="U54" s="40"/>
+      <c r="V54" s="40"/>
+      <c r="W54" s="40"/>
+      <c r="X54" s="43"/>
+      <c r="Y54" s="43"/>
+      <c r="Z54" s="40"/>
+      <c r="AA54" s="40"/>
+    </row>
+    <row r="55" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E55" s="47"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="39"/>
+      <c r="K55" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="L55" s="38"/>
-      <c r="M55" s="39"/>
-      <c r="N55" s="40"/>
-      <c r="O55" s="40"/>
-      <c r="P55" s="40"/>
-      <c r="Q55" s="40"/>
-      <c r="R55" s="40"/>
-      <c r="S55" s="42"/>
-      <c r="T55" s="41"/>
-      <c r="U55" s="41"/>
-      <c r="V55" s="41"/>
-      <c r="W55" s="41"/>
-      <c r="X55" s="44"/>
-      <c r="Y55" s="44"/>
-      <c r="Z55" s="41"/>
-      <c r="AA55" s="41"/>
-    </row>
-    <row r="56" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E56" s="48"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="38" t="s">
+      <c r="L55" s="37"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="39"/>
+      <c r="O55" s="39"/>
+      <c r="P55" s="39"/>
+      <c r="Q55" s="39"/>
+      <c r="R55" s="39"/>
+      <c r="S55" s="41"/>
+      <c r="T55" s="40"/>
+      <c r="U55" s="40"/>
+      <c r="V55" s="40"/>
+      <c r="W55" s="40"/>
+      <c r="X55" s="43"/>
+      <c r="Y55" s="43"/>
+      <c r="Z55" s="40"/>
+      <c r="AA55" s="40"/>
+    </row>
+    <row r="56" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E56" s="47"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="L56" s="38"/>
-      <c r="M56" s="39"/>
-      <c r="N56" s="40"/>
-      <c r="O56" s="40"/>
-      <c r="P56" s="40"/>
-      <c r="Q56" s="40"/>
-      <c r="R56" s="40"/>
-      <c r="S56" s="40"/>
-      <c r="T56" s="42"/>
-      <c r="U56" s="41"/>
-      <c r="V56" s="41"/>
-      <c r="W56" s="41"/>
-      <c r="X56" s="44"/>
-      <c r="Y56" s="44"/>
-      <c r="Z56" s="41"/>
-      <c r="AA56" s="41"/>
-    </row>
-    <row r="57" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E57" s="48"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40"/>
-      <c r="K57" s="38" t="s">
+      <c r="L56" s="37"/>
+      <c r="M56" s="38"/>
+      <c r="N56" s="39"/>
+      <c r="O56" s="39"/>
+      <c r="P56" s="39"/>
+      <c r="Q56" s="39"/>
+      <c r="R56" s="39"/>
+      <c r="S56" s="39"/>
+      <c r="T56" s="41"/>
+      <c r="U56" s="40"/>
+      <c r="V56" s="40"/>
+      <c r="W56" s="40"/>
+      <c r="X56" s="43"/>
+      <c r="Y56" s="43"/>
+      <c r="Z56" s="40"/>
+      <c r="AA56" s="40"/>
+    </row>
+    <row r="57" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E57" s="47"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="39"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="39"/>
+      <c r="J57" s="39"/>
+      <c r="K57" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="L57" s="38"/>
-      <c r="M57" s="39"/>
-      <c r="N57" s="40"/>
-      <c r="O57" s="40"/>
-      <c r="P57" s="40"/>
-      <c r="Q57" s="40"/>
-      <c r="R57" s="40"/>
-      <c r="S57" s="40"/>
-      <c r="T57" s="40"/>
-      <c r="U57" s="42"/>
-      <c r="V57" s="41"/>
-      <c r="W57" s="41"/>
-      <c r="X57" s="44"/>
-      <c r="Y57" s="44"/>
-      <c r="Z57" s="41"/>
-      <c r="AA57" s="41"/>
-    </row>
-    <row r="58" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E58" s="48"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="38" t="s">
+      <c r="L57" s="37"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="39"/>
+      <c r="O57" s="39"/>
+      <c r="P57" s="39"/>
+      <c r="Q57" s="39"/>
+      <c r="R57" s="39"/>
+      <c r="S57" s="39"/>
+      <c r="T57" s="39"/>
+      <c r="U57" s="41"/>
+      <c r="V57" s="40"/>
+      <c r="W57" s="40"/>
+      <c r="X57" s="43"/>
+      <c r="Y57" s="43"/>
+      <c r="Z57" s="40"/>
+      <c r="AA57" s="40"/>
+    </row>
+    <row r="58" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E58" s="47"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="L58" s="38"/>
-      <c r="M58" s="39"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="40"/>
-      <c r="P58" s="40"/>
-      <c r="Q58" s="40"/>
-      <c r="R58" s="40"/>
-      <c r="S58" s="40"/>
-      <c r="T58" s="40"/>
-      <c r="U58" s="40"/>
-      <c r="V58" s="42"/>
-      <c r="W58" s="41"/>
-      <c r="X58" s="44"/>
-      <c r="Y58" s="44"/>
-      <c r="Z58" s="41"/>
-      <c r="AA58" s="41"/>
-    </row>
-    <row r="59" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E59" s="48"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="38" t="s">
+      <c r="L58" s="37"/>
+      <c r="M58" s="38"/>
+      <c r="N58" s="39"/>
+      <c r="O58" s="39"/>
+      <c r="P58" s="39"/>
+      <c r="Q58" s="39"/>
+      <c r="R58" s="39"/>
+      <c r="S58" s="39"/>
+      <c r="T58" s="39"/>
+      <c r="U58" s="39"/>
+      <c r="V58" s="41"/>
+      <c r="W58" s="40"/>
+      <c r="X58" s="43"/>
+      <c r="Y58" s="43"/>
+      <c r="Z58" s="40"/>
+      <c r="AA58" s="40"/>
+    </row>
+    <row r="59" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E59" s="47"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="39"/>
+      <c r="K59" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="L59" s="38"/>
-      <c r="M59" s="39"/>
-      <c r="N59" s="40"/>
-      <c r="O59" s="40"/>
-      <c r="P59" s="40"/>
-      <c r="Q59" s="40"/>
-      <c r="R59" s="40"/>
-      <c r="S59" s="40"/>
-      <c r="T59" s="40"/>
-      <c r="U59" s="40"/>
-      <c r="V59" s="40"/>
-      <c r="W59" s="42"/>
-      <c r="X59" s="44"/>
-      <c r="Y59" s="44"/>
-      <c r="Z59" s="41"/>
-      <c r="AA59" s="41"/>
-    </row>
-    <row r="60" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E60" s="48"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="38" t="s">
+      <c r="L59" s="37"/>
+      <c r="M59" s="38"/>
+      <c r="N59" s="39"/>
+      <c r="O59" s="39"/>
+      <c r="P59" s="39"/>
+      <c r="Q59" s="39"/>
+      <c r="R59" s="39"/>
+      <c r="S59" s="39"/>
+      <c r="T59" s="39"/>
+      <c r="U59" s="39"/>
+      <c r="V59" s="39"/>
+      <c r="W59" s="41"/>
+      <c r="X59" s="43"/>
+      <c r="Y59" s="43"/>
+      <c r="Z59" s="40"/>
+      <c r="AA59" s="40"/>
+    </row>
+    <row r="60" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E60" s="47"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="L60" s="38"/>
-      <c r="M60" s="39"/>
-      <c r="N60" s="40"/>
-      <c r="O60" s="40"/>
-      <c r="P60" s="40"/>
-      <c r="Q60" s="40"/>
-      <c r="R60" s="40"/>
-      <c r="S60" s="40"/>
-      <c r="T60" s="40"/>
-      <c r="U60" s="40"/>
-      <c r="V60" s="40"/>
-      <c r="W60" s="40"/>
-      <c r="X60" s="45"/>
-      <c r="Y60" s="44"/>
-      <c r="Z60" s="41"/>
-      <c r="AA60" s="41"/>
-    </row>
-    <row r="61" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E61" s="48"/>
-      <c r="F61" s="43"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="40"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="40"/>
-      <c r="K61" s="38" t="s">
+      <c r="L60" s="37"/>
+      <c r="M60" s="38"/>
+      <c r="N60" s="39"/>
+      <c r="O60" s="39"/>
+      <c r="P60" s="39"/>
+      <c r="Q60" s="39"/>
+      <c r="R60" s="39"/>
+      <c r="S60" s="39"/>
+      <c r="T60" s="39"/>
+      <c r="U60" s="39"/>
+      <c r="V60" s="39"/>
+      <c r="W60" s="39"/>
+      <c r="X60" s="44"/>
+      <c r="Y60" s="43"/>
+      <c r="Z60" s="40"/>
+      <c r="AA60" s="40"/>
+    </row>
+    <row r="61" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E61" s="47"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="39"/>
+      <c r="K61" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="L61" s="38"/>
-      <c r="M61" s="39"/>
-      <c r="N61" s="40"/>
-      <c r="O61" s="40"/>
-      <c r="P61" s="40"/>
-      <c r="Q61" s="40"/>
-      <c r="R61" s="40"/>
-      <c r="S61" s="40"/>
-      <c r="T61" s="40"/>
-      <c r="U61" s="40"/>
-      <c r="V61" s="40"/>
-      <c r="W61" s="40"/>
-      <c r="X61" s="43"/>
-      <c r="Y61" s="45"/>
-      <c r="Z61" s="41"/>
-      <c r="AA61" s="41"/>
-    </row>
-    <row r="62" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E62" s="48"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="40"/>
-      <c r="K62" s="38" t="s">
+      <c r="L61" s="37"/>
+      <c r="M61" s="38"/>
+      <c r="N61" s="39"/>
+      <c r="O61" s="39"/>
+      <c r="P61" s="39"/>
+      <c r="Q61" s="39"/>
+      <c r="R61" s="39"/>
+      <c r="S61" s="39"/>
+      <c r="T61" s="39"/>
+      <c r="U61" s="39"/>
+      <c r="V61" s="39"/>
+      <c r="W61" s="39"/>
+      <c r="X61" s="42"/>
+      <c r="Y61" s="44"/>
+      <c r="Z61" s="40"/>
+      <c r="AA61" s="40"/>
+    </row>
+    <row r="62" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E62" s="47"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39"/>
+      <c r="K62" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="L62" s="38"/>
-      <c r="M62" s="39"/>
-      <c r="N62" s="40"/>
-      <c r="O62" s="40"/>
-      <c r="P62" s="40"/>
-      <c r="Q62" s="40"/>
-      <c r="R62" s="40"/>
-      <c r="S62" s="40"/>
-      <c r="T62" s="40"/>
-      <c r="U62" s="40"/>
-      <c r="V62" s="40"/>
-      <c r="W62" s="40"/>
-      <c r="X62" s="43"/>
-      <c r="Y62" s="43"/>
-      <c r="Z62" s="42"/>
-      <c r="AA62" s="41"/>
-    </row>
-    <row r="63" spans="5:27" hidden="1" x14ac:dyDescent="0.4">
-      <c r="E63" s="48"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40"/>
-      <c r="J63" s="40"/>
-      <c r="K63" s="38" t="s">
+      <c r="L62" s="37"/>
+      <c r="M62" s="38"/>
+      <c r="N62" s="39"/>
+      <c r="O62" s="39"/>
+      <c r="P62" s="39"/>
+      <c r="Q62" s="39"/>
+      <c r="R62" s="39"/>
+      <c r="S62" s="39"/>
+      <c r="T62" s="39"/>
+      <c r="U62" s="39"/>
+      <c r="V62" s="39"/>
+      <c r="W62" s="39"/>
+      <c r="X62" s="42"/>
+      <c r="Y62" s="42"/>
+      <c r="Z62" s="41"/>
+      <c r="AA62" s="40"/>
+    </row>
+    <row r="63" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E63" s="47"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
+      <c r="J63" s="39"/>
+      <c r="K63" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="L63" s="38"/>
-      <c r="M63" s="39"/>
-      <c r="N63" s="40"/>
-      <c r="O63" s="40"/>
-      <c r="P63" s="40"/>
-      <c r="Q63" s="40"/>
-      <c r="R63" s="40"/>
-      <c r="S63" s="40"/>
-      <c r="T63" s="40"/>
-      <c r="U63" s="40"/>
-      <c r="V63" s="40"/>
-      <c r="W63" s="40"/>
-      <c r="X63" s="43"/>
-      <c r="Y63" s="43"/>
-      <c r="Z63" s="40"/>
-      <c r="AA63" s="42"/>
-    </row>
-    <row r="64" spans="5:27" hidden="1" x14ac:dyDescent="0.4"/>
-    <row r="65" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L65" s="38" t="s">
+      <c r="L63" s="37"/>
+      <c r="M63" s="38"/>
+      <c r="N63" s="39"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="39"/>
+      <c r="Q63" s="39"/>
+      <c r="R63" s="39"/>
+      <c r="S63" s="39"/>
+      <c r="T63" s="39"/>
+      <c r="U63" s="39"/>
+      <c r="V63" s="39"/>
+      <c r="W63" s="39"/>
+      <c r="X63" s="42"/>
+      <c r="Y63" s="42"/>
+      <c r="Z63" s="39"/>
+      <c r="AA63" s="41"/>
+    </row>
+    <row r="64" spans="5:27" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L65" s="37" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L66" s="38" t="s">
+    <row r="66" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L66" s="37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L67" s="38" t="s">
+    <row r="67" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L67" s="37" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L68" s="38" t="s">
+    <row r="68" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L68" s="37" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L69" s="38" t="s">
+    <row r="69" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L69" s="37" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L70" s="38" t="s">
+    <row r="70" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L70" s="37" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L71" s="38" t="s">
+    <row r="71" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L71" s="37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L72" s="38" t="s">
+    <row r="72" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L72" s="37" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L73" s="38" t="s">
+    <row r="73" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L73" s="37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L74" s="38" t="s">
+    <row r="74" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L74" s="37" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L75" s="38" t="s">
+    <row r="75" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L75" s="37" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L76" s="38" t="s">
+    <row r="76" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L76" s="37" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L77" s="38" t="s">
+    <row r="77" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L77" s="37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L78" s="38" t="s">
+    <row r="78" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L78" s="37" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="12:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="L79" s="38" t="s">
+    <row r="79" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L79" s="37" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="80" spans="12:12" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="80" spans="12:12" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="d2wj9CCEuGw4Mg6otQpiYDLe9ScqX7RqQ3VxEP8wAjD/h08OAkcxvAV0OuVlGLs0lDzKZe11zE9KnrJqQ3HHBQ==" saltValue="cDUUGHebzs7qC23bO1RmFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="J15:K15"/>
     <mergeCell ref="G11:K11"/>
     <mergeCell ref="B2:B12"/>
     <mergeCell ref="B14:B45"/>
@@ -4959,11 +4993,10 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:K3"/>
-    <mergeCell ref="J15:K15"/>
   </mergeCells>
-  <conditionalFormatting sqref="G16:J16">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>SUM($G$16:$I$16)&lt;&gt;1</formula>
+  <conditionalFormatting sqref="D19:K21 D23:K43 G22:K22 D22:E22">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$C19&gt;$G$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:I44">
@@ -4971,14 +5004,14 @@
       <formula>LEN(G$47)&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G46:J46">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>LEN(G47)&lt;&gt;0</formula>
+  <conditionalFormatting sqref="G16:J16">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>SUM($G$16:$I$16)&lt;&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19:K43">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$C19&gt;$G$3</formula>
+  <conditionalFormatting sqref="G46:J46">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>LEN(G47)&lt;&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1991" yWindow="1205" count="13">
@@ -5020,10 +5053,10 @@
       <formula2>1</formula2>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Matricule" prompt="Veuillez saisir le matricule de l'étudiant." sqref="E19:E43" xr:uid="{05545D79-A9F7-415E-9E35-7C754782A697}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Identification" prompt="Veuillez saisir le nom suivi du prénom de l'étudiant." sqref="F19:F43" xr:uid="{6307AC23-55CE-40CF-A09B-D90E1E8D0103}"/>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Nombre entier" error="Défini entre 2 et 4." promptTitle="Nombre d'étudiant" prompt="Veuillez saisir le nombre d'étudiants dans l'équipe." sqref="G3:K3" xr:uid="{06102B54-0203-44AD-81A6-56F5B30E8B76}">
       <formula1>$C$20:$C$43</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Identification" prompt="Veuillez saisir le nom suivi du prénom de l'étudiant." sqref="F19:F21 F23:F43 E22" xr:uid="{6307AC23-55CE-40CF-A09B-D90E1E8D0103}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5033,162 +5066,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E086803D-69FD-4B55-9FDE-B06A5092F69F}">
   <dimension ref="B2:E29"/>
-  <sheetFormatPr defaultColWidth="9.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.61328125" style="67" customWidth="1"/>
-    <col min="2" max="2" width="9.07421875" style="67" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="67" customWidth="1"/>
-    <col min="4" max="4" width="93.53515625" style="67" customWidth="1"/>
-    <col min="5" max="5" width="2" style="67" customWidth="1"/>
-    <col min="6" max="16384" width="9.07421875" style="67"/>
+    <col min="1" max="1" width="2.5703125" style="48" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="48" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="93.5703125" style="48" customWidth="1"/>
+    <col min="5" max="5" width="2" style="48" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="48"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="B2" s="83" t="s">
+    <row r="2" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-    </row>
-    <row r="3" spans="2:5" ht="5.8" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="67" t="s">
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+    </row>
+    <row r="3" spans="2:5" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="48" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B6" s="67" t="s">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="48" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="B8" s="83" t="s">
+    <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-    </row>
-    <row r="9" spans="2:5" ht="5.8" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B10" s="67" t="s">
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+    </row>
+    <row r="9" spans="2:5" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B11" s="67">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="48">
         <v>1</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="48" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="C12" s="84"/>
-      <c r="D12" s="85" t="s">
+    <row r="12" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="C12" s="81"/>
+      <c r="D12" s="82" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B13" s="67">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="48">
         <v>2</v>
       </c>
-      <c r="C13" s="84" t="s">
+      <c r="C13" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="48" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C14" s="84"/>
-      <c r="D14" s="86" t="s">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="81"/>
+      <c r="D14" s="83" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B15" s="67">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="48">
         <v>3</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="48" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="D16" s="86" t="s">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D16" s="83" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="B18" s="83" t="s">
+    <row r="18" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-    </row>
-    <row r="19" spans="2:5" ht="5.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="20" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C20" s="116" t="s">
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+    </row>
+    <row r="19" spans="2:5" ht="5.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="117"/>
-    </row>
-    <row r="21" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C21" s="115" t="s">
+      <c r="D20" s="114"/>
+    </row>
+    <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="112" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="115"/>
-    </row>
-    <row r="22" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C22" s="118" t="s">
+      <c r="D21" s="112"/>
+    </row>
+    <row r="22" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="115" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="118"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B24" s="67">
+      <c r="D22" s="115"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="48">
         <v>1</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="48" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B25" s="67">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="48">
         <v>2</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="48" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B26" s="67">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="48">
         <v>3</v>
       </c>
-      <c r="C26" s="67" t="s">
+      <c r="C26" s="48" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C27" s="67" t="s">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="48" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B29" s="119" t="s">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="1b2l7guspijR5vFF6djmidLGLid7xH/7XN2zvKkgkfUujyKGAS/LtrXdzhf34boRC07WUYL78YWMBzjzC9RHOw==" saltValue="6m3VbwTRqvM0Jtjvfoiu/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>

--- a/énoncé/Fiche autoévaluation comparative.xlsx
+++ b/énoncé/Fiche autoévaluation comparative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\travail\KNN_project\énoncé\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD87F2A6-A506-4A56-9C32-5A92E3DA194F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01AC8EF-203C-4C09-B380-61402CECEBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="270" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1640" yWindow="3170" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Évaluation" sheetId="1" r:id="rId1"/>
@@ -1416,6 +1416,17 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1519,14 +1530,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1546,9 +1549,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0" hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1927,20 +1927,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:AA80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="48" customWidth="1"/>
     <col min="2" max="2" width="7" style="48" customWidth="1"/>
     <col min="3" max="3" width="3" style="48" customWidth="1"/>
     <col min="4" max="4" width="12" style="48" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="48" customWidth="1"/>
-    <col min="6" max="6" width="34.42578125" style="48" customWidth="1"/>
-    <col min="7" max="9" width="13.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" style="3" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="34.453125" style="48" customWidth="1"/>
+    <col min="7" max="9" width="13.7265625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.7265625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.453125" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.26953125" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="22" width="9" style="2" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="10" style="2" hidden="1" customWidth="1"/>
     <col min="24" max="25" width="9" style="48" hidden="1" customWidth="1"/>
@@ -1948,129 +1948,129 @@
     <col min="28" max="16384" width="9" style="48"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="86" t="s">
+    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="89" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86"/>
-      <c r="D3" s="106" t="s">
+    <row r="3" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="89"/>
+      <c r="D3" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="108">
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="111">
         <v>5</v>
       </c>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="109"/>
-    </row>
-    <row r="4" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="86"/>
-    </row>
-    <row r="5" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="86"/>
-      <c r="D5" s="106" t="s">
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="112"/>
+    </row>
+    <row r="4" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="89"/>
+    </row>
+    <row r="5" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="89"/>
+      <c r="D5" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="90">
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="93">
         <v>0.85</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="91"/>
-    </row>
-    <row r="6" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="86"/>
-      <c r="G6" s="92" t="s">
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="94"/>
+    </row>
+    <row r="6" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="89"/>
+      <c r="G6" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B7" s="86"/>
-      <c r="D7" s="104" t="s">
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B7" s="89"/>
+      <c r="D7" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="93">
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="96">
         <v>0.5</v>
       </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="94"/>
-    </row>
-    <row r="8" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="86"/>
-      <c r="D8" s="102" t="s">
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="97"/>
+    </row>
+    <row r="8" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="89"/>
+      <c r="D8" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="95">
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="98">
         <f>1-G7</f>
         <v>0.5</v>
       </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="95"/>
-      <c r="K8" s="96"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="99"/>
       <c r="V8" s="4"/>
     </row>
-    <row r="9" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="86"/>
+    <row r="9" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="89"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="97"/>
-      <c r="J9" s="97"/>
-      <c r="K9" s="97"/>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B10" s="86"/>
-      <c r="D10" s="100" t="s">
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B10" s="89"/>
+      <c r="D10" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="88">
-        <v>0</v>
-      </c>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="89"/>
-    </row>
-    <row r="11" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="86"/>
-      <c r="D11" s="98" t="s">
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="91">
+        <v>0</v>
+      </c>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="92"/>
+    </row>
+    <row r="11" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="89"/>
+      <c r="D11" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="84">
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="87">
         <f ca="1">V44</f>
         <v>0</v>
       </c>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="85"/>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B12" s="86"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="88"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B12" s="89"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -2078,18 +2078,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
+    <row r="14" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="90" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="2:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="87"/>
+    <row r="15" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="90"/>
       <c r="D15" s="21"/>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
@@ -2102,13 +2102,13 @@
       <c r="I15" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="110" t="s">
+      <c r="J15" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="K15" s="111"/>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="87"/>
+      <c r="K15" s="86"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B16" s="90"/>
       <c r="D16" s="12"/>
       <c r="E16" s="13"/>
       <c r="F16" s="50" t="s">
@@ -2126,8 +2126,8 @@
       <c r="J16" s="61"/>
       <c r="K16" s="14"/>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B17" s="87"/>
+    <row r="17" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B17" s="90"/>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
       <c r="F17" s="50" t="s">
@@ -2145,8 +2145,8 @@
       <c r="J17" s="9"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="87"/>
+    <row r="18" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="90"/>
       <c r="D18" s="12"/>
       <c r="E18" s="52" t="s">
         <v>51</v>
@@ -2160,8 +2160,8 @@
       <c r="J18" s="9"/>
       <c r="K18" s="14"/>
     </row>
-    <row r="19" spans="2:27" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="87"/>
+    <row r="19" spans="2:27" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="90"/>
       <c r="C19" s="57">
         <v>1</v>
       </c>
@@ -2253,8 +2253,8 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B20" s="87"/>
+    <row r="20" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B20" s="90"/>
       <c r="C20" s="57">
         <v>2</v>
       </c>
@@ -2346,8 +2346,8 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B21" s="87"/>
+    <row r="21" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B21" s="90"/>
       <c r="C21" s="57">
         <v>3</v>
       </c>
@@ -2439,16 +2439,18 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B22" s="87"/>
+    <row r="22" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B22" s="90"/>
       <c r="C22" s="57">
         <v>4</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="65"/>
-      <c r="F22" s="117" t="s">
+      <c r="E22" s="65">
+        <v>2103613</v>
+      </c>
+      <c r="F22" s="84" t="s">
         <v>99</v>
       </c>
       <c r="G22" s="30">
@@ -2530,8 +2532,8 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B23" s="87"/>
+    <row r="23" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B23" s="90"/>
       <c r="C23" s="57">
         <v>5</v>
       </c>
@@ -2623,8 +2625,8 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B24" s="87"/>
+    <row r="24" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B24" s="90"/>
       <c r="C24" s="57">
         <v>6</v>
       </c>
@@ -2706,8 +2708,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B25" s="87"/>
+    <row r="25" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B25" s="90"/>
       <c r="C25" s="57">
         <v>7</v>
       </c>
@@ -2789,8 +2791,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B26" s="87"/>
+    <row r="26" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B26" s="90"/>
       <c r="C26" s="57">
         <v>8</v>
       </c>
@@ -2872,8 +2874,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B27" s="87"/>
+    <row r="27" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B27" s="90"/>
       <c r="C27" s="57">
         <v>9</v>
       </c>
@@ -2955,8 +2957,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B28" s="87"/>
+    <row r="28" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B28" s="90"/>
       <c r="C28" s="57">
         <v>10</v>
       </c>
@@ -3038,8 +3040,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="87"/>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B29" s="90"/>
       <c r="C29" s="57">
         <v>11</v>
       </c>
@@ -3121,8 +3123,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B30" s="87"/>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B30" s="90"/>
       <c r="C30" s="57">
         <v>12</v>
       </c>
@@ -3204,8 +3206,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B31" s="87"/>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B31" s="90"/>
       <c r="C31" s="57">
         <v>13</v>
       </c>
@@ -3287,8 +3289,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B32" s="87"/>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B32" s="90"/>
       <c r="C32" s="57">
         <v>14</v>
       </c>
@@ -3370,8 +3372,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B33" s="87"/>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B33" s="90"/>
       <c r="C33" s="57">
         <v>15</v>
       </c>
@@ -3453,8 +3455,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B34" s="87"/>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B34" s="90"/>
       <c r="C34" s="57">
         <v>16</v>
       </c>
@@ -3536,8 +3538,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B35" s="87"/>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B35" s="90"/>
       <c r="C35" s="57">
         <v>17</v>
       </c>
@@ -3619,8 +3621,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B36" s="87"/>
+    <row r="36" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B36" s="90"/>
       <c r="C36" s="57">
         <v>18</v>
       </c>
@@ -3702,8 +3704,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B37" s="87"/>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B37" s="90"/>
       <c r="C37" s="57">
         <v>19</v>
       </c>
@@ -3785,8 +3787,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B38" s="87"/>
+    <row r="38" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B38" s="90"/>
       <c r="C38" s="57">
         <v>20</v>
       </c>
@@ -3868,8 +3870,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B39" s="87"/>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B39" s="90"/>
       <c r="C39" s="57">
         <v>21</v>
       </c>
@@ -3951,8 +3953,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B40" s="87"/>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B40" s="90"/>
       <c r="C40" s="57">
         <v>22</v>
       </c>
@@ -4034,8 +4036,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B41" s="87"/>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B41" s="90"/>
       <c r="C41" s="57">
         <v>23</v>
       </c>
@@ -4117,8 +4119,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B42" s="87"/>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B42" s="90"/>
       <c r="C42" s="57">
         <v>24</v>
       </c>
@@ -4200,8 +4202,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="43" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="87"/>
+    <row r="43" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="90"/>
       <c r="C43" s="57">
         <v>25</v>
       </c>
@@ -4283,8 +4285,8 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="44" spans="2:27" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="87"/>
+    <row r="44" spans="2:27" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="90"/>
       <c r="D44" s="19"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
@@ -4334,8 +4336,8 @@
       <c r="X44" s="2"/>
       <c r="Y44" s="2"/>
     </row>
-    <row r="45" spans="2:27" s="6" customFormat="1" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="87"/>
+    <row r="45" spans="2:27" s="6" customFormat="1" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="90"/>
       <c r="G45" s="53"/>
       <c r="H45" s="36"/>
       <c r="I45" s="36"/>
@@ -4377,7 +4379,7 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="2:27" s="6" customFormat="1" ht="12.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:27" s="6" customFormat="1" ht="12.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="54"/>
       <c r="G46" s="56" t="s">
         <v>52</v>
@@ -4406,7 +4408,7 @@
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
     </row>
-    <row r="47" spans="2:27" s="6" customFormat="1" ht="31.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:27" s="6" customFormat="1" ht="31.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G47" s="55" t="str">
         <f ca="1">IF(G44&lt;&gt;1,"La somme doit être égale à 100%","")</f>
         <v/>
@@ -4437,7 +4439,7 @@
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
     </row>
-    <row r="48" spans="2:27" s="6" customFormat="1" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:27" s="6" customFormat="1" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H48" s="36"/>
       <c r="I48" s="36"/>
       <c r="J48" s="36"/>
@@ -4488,7 +4490,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E49" s="42"/>
       <c r="F49" s="42"/>
       <c r="G49" s="39"/>
@@ -4518,7 +4520,7 @@
       <c r="Z49" s="40"/>
       <c r="AA49" s="40"/>
     </row>
-    <row r="50" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E50" s="47"/>
       <c r="F50" s="42"/>
       <c r="G50" s="39"/>
@@ -4545,7 +4547,7 @@
       <c r="Z50" s="40"/>
       <c r="AA50" s="40"/>
     </row>
-    <row r="51" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E51" s="47"/>
       <c r="F51" s="42"/>
       <c r="G51" s="39"/>
@@ -4572,7 +4574,7 @@
       <c r="Z51" s="40"/>
       <c r="AA51" s="40"/>
     </row>
-    <row r="52" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E52" s="47"/>
       <c r="F52" s="42"/>
       <c r="G52" s="39"/>
@@ -4599,7 +4601,7 @@
       <c r="Z52" s="40"/>
       <c r="AA52" s="40"/>
     </row>
-    <row r="53" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E53" s="47"/>
       <c r="F53" s="42"/>
       <c r="G53" s="39"/>
@@ -4626,7 +4628,7 @@
       <c r="Z53" s="40"/>
       <c r="AA53" s="40"/>
     </row>
-    <row r="54" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E54" s="47"/>
       <c r="F54" s="42"/>
       <c r="G54" s="39"/>
@@ -4653,7 +4655,7 @@
       <c r="Z54" s="40"/>
       <c r="AA54" s="40"/>
     </row>
-    <row r="55" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E55" s="47"/>
       <c r="F55" s="42"/>
       <c r="G55" s="39"/>
@@ -4680,7 +4682,7 @@
       <c r="Z55" s="40"/>
       <c r="AA55" s="40"/>
     </row>
-    <row r="56" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E56" s="47"/>
       <c r="F56" s="42"/>
       <c r="G56" s="39"/>
@@ -4707,7 +4709,7 @@
       <c r="Z56" s="40"/>
       <c r="AA56" s="40"/>
     </row>
-    <row r="57" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E57" s="47"/>
       <c r="F57" s="42"/>
       <c r="G57" s="39"/>
@@ -4734,7 +4736,7 @@
       <c r="Z57" s="40"/>
       <c r="AA57" s="40"/>
     </row>
-    <row r="58" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E58" s="47"/>
       <c r="F58" s="42"/>
       <c r="G58" s="39"/>
@@ -4761,7 +4763,7 @@
       <c r="Z58" s="40"/>
       <c r="AA58" s="40"/>
     </row>
-    <row r="59" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E59" s="47"/>
       <c r="F59" s="42"/>
       <c r="G59" s="39"/>
@@ -4788,7 +4790,7 @@
       <c r="Z59" s="40"/>
       <c r="AA59" s="40"/>
     </row>
-    <row r="60" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E60" s="47"/>
       <c r="F60" s="42"/>
       <c r="G60" s="39"/>
@@ -4815,7 +4817,7 @@
       <c r="Z60" s="40"/>
       <c r="AA60" s="40"/>
     </row>
-    <row r="61" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E61" s="47"/>
       <c r="F61" s="42"/>
       <c r="G61" s="39"/>
@@ -4842,7 +4844,7 @@
       <c r="Z61" s="40"/>
       <c r="AA61" s="40"/>
     </row>
-    <row r="62" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E62" s="47"/>
       <c r="F62" s="42"/>
       <c r="G62" s="39"/>
@@ -4869,7 +4871,7 @@
       <c r="Z62" s="41"/>
       <c r="AA62" s="40"/>
     </row>
-    <row r="63" spans="5:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="5:27" hidden="1" x14ac:dyDescent="0.35">
       <c r="E63" s="47"/>
       <c r="F63" s="42"/>
       <c r="G63" s="39"/>
@@ -4896,86 +4898,87 @@
       <c r="Z63" s="39"/>
       <c r="AA63" s="41"/>
     </row>
-    <row r="64" spans="5:27" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="5:27" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="65" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L65" s="37" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L66" s="37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L67" s="37" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L68" s="37" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L69" s="37" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L70" s="37" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L71" s="37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L72" s="37" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L73" s="37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L74" s="37" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L75" s="37" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L76" s="37" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L77" s="37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L78" s="37" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="12:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="12:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="L79" s="37" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="80" spans="12:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="12:12" hidden="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="d2wj9CCEuGw4Mg6otQpiYDLe9ScqX7RqQ3VxEP8wAjD/h08OAkcxvAV0OuVlGLs0lDzKZe11zE9KnrJqQ3HHBQ==" saltValue="cDUUGHebzs7qC23bO1RmFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="G3:K3"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="G11:K11"/>
     <mergeCell ref="B2:B12"/>
@@ -4992,9 +4995,8 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:K3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D19:K21 D23:K43 G22:K22 D22:E22">
+  <conditionalFormatting sqref="D19:K21 D22:E22 G22:K22 D23:K43">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$C19&gt;$G$3</formula>
     </cfRule>
@@ -5066,17 +5068,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E086803D-69FD-4B55-9FDE-B06A5092F69F}">
   <dimension ref="B2:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="48" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="48" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="48" customWidth="1"/>
-    <col min="4" max="4" width="93.5703125" style="48" customWidth="1"/>
+    <col min="1" max="1" width="2.54296875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="48" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="93.54296875" style="48" customWidth="1"/>
     <col min="5" max="5" width="2" style="48" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="48"/>
+    <col min="6" max="16384" width="9.1796875" style="48"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="80" t="s">
         <v>93</v>
       </c>
@@ -5084,18 +5086,18 @@
       <c r="D2" s="80"/>
       <c r="E2" s="80"/>
     </row>
-    <row r="3" spans="2:5" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" ht="5.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="48" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="48" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B8" s="80" t="s">
         <v>94</v>
       </c>
@@ -5103,13 +5105,13 @@
       <c r="D8" s="80"/>
       <c r="E8" s="80"/>
     </row>
-    <row r="9" spans="2:5" ht="5.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" ht="5.9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="48">
         <v>1</v>
       </c>
@@ -5120,13 +5122,13 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" ht="29" x14ac:dyDescent="0.35">
       <c r="C12" s="81"/>
       <c r="D12" s="82" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="48">
         <v>2</v>
       </c>
@@ -5137,13 +5139,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C14" s="81"/>
       <c r="D14" s="83" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="48">
         <v>3</v>
       </c>
@@ -5154,12 +5156,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D16" s="83" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B18" s="80" t="s">
         <v>85</v>
       </c>
@@ -5167,26 +5169,26 @@
       <c r="D18" s="80"/>
       <c r="E18" s="80"/>
     </row>
-    <row r="19" spans="2:5" ht="5.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="113" t="s">
+    <row r="19" spans="2:5" ht="5.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C20" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="114"/>
-    </row>
-    <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="112" t="s">
+      <c r="D20" s="115"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C21" s="113" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="112"/>
-    </row>
-    <row r="22" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="115" t="s">
+      <c r="D21" s="113"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C22" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="115"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D22" s="116"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="48">
         <v>1</v>
       </c>
@@ -5194,7 +5196,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="48">
         <v>2</v>
       </c>
@@ -5202,7 +5204,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="48">
         <v>3</v>
       </c>
@@ -5210,18 +5212,18 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C27" s="48" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="116" t="s">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B29" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="1b2l7guspijR5vFF6djmidLGLid7xH/7XN2zvKkgkfUujyKGAS/LtrXdzhf34boRC07WUYL78YWMBzjzC9RHOw==" saltValue="6m3VbwTRqvM0Jtjvfoiu/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
